--- a/output/北塩原村_圏域サービス資源.xlsx
+++ b/output/北塩原村_圏域サービス資源.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ReMHRAD（地域精神保健福祉資源分析データベース）の障害福祉資源による、市町村別事業所数の2020年から2025年への推移。事業所数は所在地の市町村でカウントされるため、本村の住民が圏域外の事業所を利用している分はこの表には現れない。</t>
+          <t>ReMHRAD 障害福祉資源による市町村別事業所数の2020年から2025年への推移。出典は障害福祉サービス等情報公表システム（障害種を問わない全施設）2025年度分。事業所数は所在地の市町村でカウントされるため、本村の住民が圏域外の事業所を利用している分はこの表には現れない。</t>
         </is>
       </c>
     </row>
@@ -722,13 +722,21 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>出典の障害福祉サービス等情報公表システムに公表されていない事業所は計上されません。第8期基本指針が公表率・更新率100%を成果目標に新設したのは、この網羅性の問題への対処です（第二の八）。村の指定・委託の記録と突き合わせて確認してください。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
